--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488109_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488109_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2932</v>
+        <v>1.208</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0212</v>
+        <v>1.208</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7281</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.0364</v>
+        <v>1.208</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1595</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.8769</v>
+        <v>0.6027</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.6136</v>
+        <v>1.208</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.055</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5586</v>
+        <v>0.6027</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4228</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1044</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3184</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1639</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1345</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.2985</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8988</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>4.4914</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.208</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.208</v>
+        <v>1.9007</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1.1946</v>
       </c>
       <c r="G3" t="n">
-        <v>1.208</v>
+        <v>-3.0364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.1595</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6027</v>
+        <v>-1.8769</v>
       </c>
       <c r="J3" t="n">
-        <v>1.208</v>
+        <v>-1.6136</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6027</v>
+        <v>-0.5586</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1.4228</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.1044</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-1.3184</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.751</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1.765</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.8988</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.4914</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3691</v>
+        <v>0.4533</v>
       </c>
       <c r="E4" t="n">
         <v>-0.0844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4535</v>
+        <v>0.5377</v>
       </c>
       <c r="G4" t="n">
         <v>0.1801</v>
@@ -766,13 +766,13 @@
         <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4761</v>
+        <v>-0.3919</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3513</v>
+        <v>-0.2671</v>
       </c>
       <c r="V4" t="n">
         <v>0.0704</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3031</v>
+        <v>0.2371</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1965</v>
+        <v>1.7515</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8935</v>
+        <v>-1.5144</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8758</v>
+        <v>2.9876</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3357</v>
+        <v>1.7726</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4599</v>
+        <v>1.2149</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1596</v>
+        <v>3.1059</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8387</v>
+        <v>1.8967</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6791</v>
+        <v>1.2092</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2838</v>
+        <v>-0.1184</v>
       </c>
       <c r="N5" t="n">
-        <v>0.497</v>
+        <v>-0.1241</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.0057</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9822</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4738</v>
+        <v>-1.149</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6425999999999999</v>
+        <v>-0.3634</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1688</v>
+        <v>-0.7857</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.0287</v>
+        <v>-1.4033</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.6213</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.287</v>
+        <v>-0.4736</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6891</v>
+        <v>1.9533</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4021</v>
+        <v>-2.4269</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9876</v>
+        <v>1.8758</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7726</v>
+        <v>3.3357</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2149</v>
+        <v>-1.4599</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1059</v>
+        <v>2.1596</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8967</v>
+        <v>2.8387</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2092</v>
+        <v>-0.6791</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1184</v>
+        <v>-0.2838</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1241</v>
+        <v>0.497</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0057</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P6" t="n">
+        <v>1.9822</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.1982</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.9911</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0991</v>
+        <v>-0.3029</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4257</v>
+        <v>0.3994</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6733</v>
+        <v>-0.7023</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4033</v>
+        <v>-4.0287</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4033</v>
+        <v>-3.6213</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8226</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0952</v>
+        <v>-2.9309</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2725</v>
+        <v>2.1602</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1339</v>
@@ -1000,13 +1000,13 @@
         <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0456</v>
+        <v>0.0064</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3634</v>
+        <v>-0.1991</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3178</v>
+        <v>0.2055</v>
       </c>
       <c r="V7" t="n">
         <v>1.3479</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.686</v>
+        <v>-1.2828</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0429</v>
+        <v>0.5288</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6431</v>
+        <v>-1.8116</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3734</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.381</v>
+        <v>-1.9778</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1745</v>
+        <v>-0.6028</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2065</v>
+        <v>-1.375</v>
       </c>
       <c r="V8" t="n">
         <v>1.4737</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0091</v>
+        <v>-1.4997</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1909</v>
+        <v>-0.6815</v>
       </c>
       <c r="F9" t="n">
         <v>-0.8182</v>
@@ -1156,10 +1156,10 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.964</v>
+        <v>-1.4546</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.4156</v>
       </c>
       <c r="U9" t="n">
         <v>-1.039</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0778</v>
+        <v>-2.3624</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.795</v>
+        <v>-1.5289</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2828</v>
+        <v>-0.8335</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3058</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.9969</v>
+        <v>-2.2815</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4109</v>
+        <v>-0.1448</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.5859</v>
+        <v>-2.1367</v>
       </c>
       <c r="V10" t="n">
         <v>3.0178</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4578</v>
+        <v>-5.4963</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.592</v>
+        <v>-4.4901</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8658</v>
+        <v>-1.0062</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7558</v>
@@ -1312,13 +1312,13 @@
         <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2044</v>
+        <v>-2.2429</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2972</v>
+        <v>-0.1953</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9073</v>
+        <v>-2.0476</v>
       </c>
       <c r="V11" t="n">
         <v>1.8811</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.5929</v>
+        <v>-9.280999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6856</v>
+        <v>-2.373499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.9076</v>
+        <v>-6.9075</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.251300000000001</v>
+        <v>-6.2513</v>
       </c>
       <c r="H12" t="n">
         <v>3.7646</v>
@@ -1390,13 +1390,13 @@
         <v>13.8757</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.8572</v>
+        <v>-11.5452</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9443</v>
+        <v>-1.6324</v>
       </c>
       <c r="U12" t="n">
-        <v>-9.912799999999999</v>
+        <v>-9.9129</v>
       </c>
       <c r="V12" t="n">
         <v>7.5243</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1067</v>
+        <v>3.9191</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7116</v>
+        <v>2.591</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3951</v>
+        <v>1.3281</v>
       </c>
       <c r="G13" t="n">
         <v>1.1437</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>5.305</v>
+        <v>3.1174</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8561</v>
+        <v>1.7356</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4489</v>
+        <v>1.3819</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1438</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. WRIGHT RODRIGUEZ</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3459</v>
+        <v>3.3551</v>
       </c>
       <c r="E14" t="n">
-        <v>2.944</v>
+        <v>1.8432</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4019</v>
+        <v>1.5119</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3971</v>
+        <v>3.1929</v>
       </c>
       <c r="H14" t="n">
-        <v>0.13</v>
+        <v>-0.3391</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2671</v>
+        <v>3.532</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1001</v>
+        <v>2.0207</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6536999999999999</v>
+        <v>-0.2888</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4464</v>
+        <v>2.3096</v>
       </c>
       <c r="M14" t="n">
-        <v>0.297</v>
+        <v>1.1722</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.0503</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8207</v>
+        <v>1.2224</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.1805</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7021</v>
+        <v>1.0839</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3723</v>
+        <v>0.7958</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3298</v>
+        <v>0.288</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.555</v>
+        <v>-0.1288</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.3479</v>
+        <v>1.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2071</v>
+        <v>-1.3359</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8131</v>
+        <v>3.0774</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7413</v>
+        <v>1.7324</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0718</v>
+        <v>1.345</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1929</v>
+        <v>-0.4837</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3391</v>
+        <v>-1.096</v>
       </c>
       <c r="I15" t="n">
-        <v>3.532</v>
+        <v>0.6123</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0207</v>
+        <v>0.019</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2888</v>
+        <v>-0.712</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3096</v>
+        <v>0.731</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1722</v>
+        <v>-0.5027</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0503</v>
+        <v>-0.3839</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2224</v>
+        <v>-0.1187</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5419</v>
+        <v>1.6235</v>
       </c>
       <c r="T15" t="n">
-        <v>0.694</v>
+        <v>1.2309</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1521</v>
+        <v>0.3927</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1288</v>
+        <v>1.5411</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3359</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7729</v>
+        <v>2.3617</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8862</v>
+        <v>2.0068</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1133</v>
+        <v>0.3549</v>
       </c>
       <c r="G16" t="n">
         <v>1.0384</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1941</v>
+        <v>0.3946</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7488</v>
+        <v>0.3718</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4454</v>
+        <v>0.0228</v>
       </c>
       <c r="V16" t="n">
         <v>0.334</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>D. WRIGHT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7161</v>
+        <v>1.5922</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2044</v>
+        <v>0.0917</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5117</v>
+        <v>1.5005</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4837</v>
+        <v>2.3971</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.096</v>
+        <v>0.13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6123</v>
+        <v>2.2671</v>
       </c>
       <c r="J17" t="n">
-        <v>0.019</v>
+        <v>2.1001</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.712</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.731</v>
+        <v>1.4464</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5027</v>
+        <v>0.297</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3839</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1187</v>
+        <v>0.8207</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7377</v>
+        <v>1.9484</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2972</v>
+        <v>1.5199</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4406</v>
+        <v>0.4284</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5411</v>
+        <v>-2.555</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4737</v>
+        <v>-1.3479</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.9127</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.7049</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-1.7922</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.5468</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.2155</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.2469</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.6855</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.9324</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.5782</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.8613</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.7355</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.3896</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3459</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.6808</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5012</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8999</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6687</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5468</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2155</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2469</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6855</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9324</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5782</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8613</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.424</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1859</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2381</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6808</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.9474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5043</v>
+        <v>-0.392</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1196</v>
+        <v>0.2319</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0367</v>
@@ -2014,13 +2014,13 @@
         <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8516</v>
+        <v>1.964</v>
       </c>
       <c r="T20" t="n">
         <v>1.7364</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1152</v>
+        <v>0.2275</v>
       </c>
       <c r="V20" t="n">
         <v>-0.337</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3836</v>
+        <v>-1.5758</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3077</v>
+        <v>-3.104</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9242</v>
+        <v>1.5282</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4742</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1531</v>
+        <v>0.9609</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2461</v>
+        <v>0.4499</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.093</v>
+        <v>0.511</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8731</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4804</v>
+        <v>-2.2253</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7549</v>
+        <v>-0.9399</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7255</v>
+        <v>-1.2854</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8003</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1886</v>
+        <v>1.0664</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.132</v>
+        <v>0.6829</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0566</v>
+        <v>0.3835</v>
       </c>
       <c r="V22" t="n">
         <v>-2.6808</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.593000000000002</v>
+        <v>11.6304</v>
       </c>
       <c r="E23" t="n">
-        <v>6.907499999999998</v>
+        <v>6.9075</v>
       </c>
       <c r="F23" t="n">
-        <v>2.685599999999999</v>
+        <v>4.722899999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>6.251200000000001</v>
+        <v>6.251199999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.7649</v>
+        <v>-3.764899999999999</v>
       </c>
       <c r="I23" t="n">
         <v>10.016</v>
@@ -2248,13 +2248,13 @@
         <v>12.8845</v>
       </c>
       <c r="S23" t="n">
-        <v>11.8573</v>
+        <v>13.8946</v>
       </c>
       <c r="T23" t="n">
         <v>9.912800000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9443</v>
+        <v>3.9817</v>
       </c>
       <c r="V23" t="n">
         <v>-7.5242</v>
